--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_ADG.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_ADG.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T2" t="n">
         <v>3</v>
@@ -663,10 +663,10 @@
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
